--- a/data_lake/datos_diarios_preliminares/dt=2026-09-13/Temp-max-septiembre-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-09-13/Temp-max-septiembre-26.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3931D9C9-7F7F-461B-BA82-2C3F32EB4F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E090C99-C0BF-40F4-B4AC-EB4259CB13B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TMAX_PRINCIPALES_CIUDADES" sheetId="1" r:id="rId1"/>
@@ -9456,7 +9456,9 @@
       <c r="O5" s="63">
         <v>32.700000000000003</v>
       </c>
-      <c r="P5" s="63"/>
+      <c r="P5" s="63">
+        <v>32.4</v>
+      </c>
       <c r="Q5" s="63"/>
       <c r="R5" s="63"/>
       <c r="S5" s="63"/>
@@ -9478,7 +9480,7 @@
       <c r="AI5" s="63"/>
       <c r="AJ5" s="36">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>32.700000000000003</v>
+        <v>32.4</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9551,7 +9553,9 @@
       <c r="O6" s="63">
         <v>32.200000000000003</v>
       </c>
-      <c r="P6" s="63"/>
+      <c r="P6" s="63">
+        <v>32.5</v>
+      </c>
       <c r="Q6" s="63"/>
       <c r="R6" s="63"/>
       <c r="S6" s="63"/>
@@ -9573,7 +9577,7 @@
       <c r="AI6" s="63"/>
       <c r="AJ6" s="36">
         <f t="shared" ref="AJ6:AJ48" si="1">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>32.200000000000003</v>
+        <v>32.5</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="2">+MAX($E6:$AI6)</f>
@@ -9646,7 +9650,9 @@
       <c r="O7" s="63">
         <v>35.200000000000003</v>
       </c>
-      <c r="P7" s="63"/>
+      <c r="P7" s="63">
+        <v>35.4</v>
+      </c>
       <c r="Q7" s="63"/>
       <c r="R7" s="63"/>
       <c r="S7" s="63"/>
@@ -9668,7 +9674,7 @@
       <c r="AI7" s="63"/>
       <c r="AJ7" s="36">
         <f t="shared" si="1"/>
-        <v>35.200000000000003</v>
+        <v>35.4</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="2"/>
@@ -9741,7 +9747,9 @@
       <c r="O8" s="63">
         <v>32.799999999999997</v>
       </c>
-      <c r="P8" s="63"/>
+      <c r="P8" s="63">
+        <v>34.6</v>
+      </c>
       <c r="Q8" s="63"/>
       <c r="R8" s="63"/>
       <c r="S8" s="63"/>
@@ -9763,7 +9771,7 @@
       <c r="AI8" s="63"/>
       <c r="AJ8" s="36">
         <f t="shared" si="1"/>
-        <v>32.799999999999997</v>
+        <v>34.6</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="2"/>
@@ -9836,7 +9844,9 @@
       <c r="O9" s="63">
         <v>34.700000000000003</v>
       </c>
-      <c r="P9" s="63"/>
+      <c r="P9" s="63">
+        <v>34.9</v>
+      </c>
       <c r="Q9" s="63"/>
       <c r="R9" s="63"/>
       <c r="S9" s="63"/>
@@ -9858,7 +9868,7 @@
       <c r="AI9" s="63"/>
       <c r="AJ9" s="36">
         <f t="shared" si="1"/>
-        <v>34.700000000000003</v>
+        <v>34.9</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="2"/>
@@ -9931,7 +9941,9 @@
       <c r="O10" s="63">
         <v>36.5</v>
       </c>
-      <c r="P10" s="63"/>
+      <c r="P10" s="63">
+        <v>36.200000000000003</v>
+      </c>
       <c r="Q10" s="63"/>
       <c r="R10" s="63"/>
       <c r="S10" s="63"/>
@@ -9953,7 +9965,7 @@
       <c r="AI10" s="63"/>
       <c r="AJ10" s="36">
         <f t="shared" si="1"/>
-        <v>36.5</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="2"/>
@@ -10026,7 +10038,9 @@
       <c r="O11" s="63">
         <v>38.9</v>
       </c>
-      <c r="P11" s="63"/>
+      <c r="P11" s="63">
+        <v>37.5</v>
+      </c>
       <c r="Q11" s="63"/>
       <c r="R11" s="63"/>
       <c r="S11" s="63"/>
@@ -10048,7 +10062,7 @@
       <c r="AI11" s="63"/>
       <c r="AJ11" s="36">
         <f t="shared" si="1"/>
-        <v>38.9</v>
+        <v>37.5</v>
       </c>
       <c r="AK11" s="21">
         <f t="shared" si="2"/>
@@ -10121,7 +10135,9 @@
       <c r="O12" s="63">
         <v>32.6</v>
       </c>
-      <c r="P12" s="63"/>
+      <c r="P12" s="63">
+        <v>35</v>
+      </c>
       <c r="Q12" s="63"/>
       <c r="R12" s="63"/>
       <c r="S12" s="63"/>
@@ -10143,7 +10159,7 @@
       <c r="AI12" s="63"/>
       <c r="AJ12" s="36">
         <f t="shared" si="1"/>
-        <v>32.6</v>
+        <v>35</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="2"/>
@@ -10216,7 +10232,9 @@
       <c r="O13" s="63">
         <v>33.6</v>
       </c>
-      <c r="P13" s="63"/>
+      <c r="P13" s="63">
+        <v>36</v>
+      </c>
       <c r="Q13" s="63"/>
       <c r="R13" s="63"/>
       <c r="S13" s="63"/>
@@ -10238,7 +10256,7 @@
       <c r="AI13" s="63"/>
       <c r="AJ13" s="36">
         <f t="shared" si="1"/>
-        <v>33.6</v>
+        <v>36</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="2"/>
@@ -10311,7 +10329,9 @@
       <c r="O14" s="63">
         <v>31.9</v>
       </c>
-      <c r="P14" s="63"/>
+      <c r="P14" s="63">
+        <v>35.5</v>
+      </c>
       <c r="Q14" s="63"/>
       <c r="R14" s="63"/>
       <c r="S14" s="63"/>
@@ -10333,7 +10353,7 @@
       <c r="AI14" s="63"/>
       <c r="AJ14" s="36">
         <f t="shared" si="1"/>
-        <v>31.9</v>
+        <v>35.5</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="2"/>
@@ -10406,7 +10426,9 @@
       <c r="O15" s="63">
         <v>29.9</v>
       </c>
-      <c r="P15" s="63"/>
+      <c r="P15" s="63">
+        <v>32.200000000000003</v>
+      </c>
       <c r="Q15" s="63"/>
       <c r="R15" s="63"/>
       <c r="S15" s="63"/>
@@ -10428,7 +10450,7 @@
       <c r="AI15" s="63"/>
       <c r="AJ15" s="36">
         <f t="shared" si="1"/>
-        <v>29.9</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="2"/>
@@ -10550,7 +10572,9 @@
       <c r="O17" s="63">
         <v>33</v>
       </c>
-      <c r="P17" s="63"/>
+      <c r="P17" s="63">
+        <v>36.5</v>
+      </c>
       <c r="Q17" s="63"/>
       <c r="R17" s="63"/>
       <c r="S17" s="63"/>
@@ -10572,7 +10596,7 @@
       <c r="AI17" s="63"/>
       <c r="AJ17" s="36">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>36.5</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="2"/>
@@ -10645,7 +10669,9 @@
       <c r="O18" s="63">
         <v>28.6</v>
       </c>
-      <c r="P18" s="63"/>
+      <c r="P18" s="63">
+        <v>29.1</v>
+      </c>
       <c r="Q18" s="63"/>
       <c r="R18" s="63"/>
       <c r="S18" s="63"/>
@@ -10667,7 +10693,7 @@
       <c r="AI18" s="63"/>
       <c r="AJ18" s="36">
         <f t="shared" si="1"/>
-        <v>28.6</v>
+        <v>29.1</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="2"/>
@@ -10740,7 +10766,9 @@
       <c r="O19" s="63">
         <v>35.5</v>
       </c>
-      <c r="P19" s="63"/>
+      <c r="P19" s="63">
+        <v>36.700000000000003</v>
+      </c>
       <c r="Q19" s="63"/>
       <c r="R19" s="63"/>
       <c r="S19" s="63"/>
@@ -10762,7 +10790,7 @@
       <c r="AI19" s="63"/>
       <c r="AJ19" s="36">
         <f t="shared" si="1"/>
-        <v>35.5</v>
+        <v>36.700000000000003</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="2"/>
@@ -10835,7 +10863,9 @@
       <c r="O20" s="63">
         <v>29</v>
       </c>
-      <c r="P20" s="63"/>
+      <c r="P20" s="63">
+        <v>31.3</v>
+      </c>
       <c r="Q20" s="63"/>
       <c r="R20" s="63"/>
       <c r="S20" s="63"/>
@@ -10857,7 +10887,7 @@
       <c r="AI20" s="63"/>
       <c r="AJ20" s="36">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>31.3</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="2"/>
@@ -10930,7 +10960,9 @@
       <c r="O21" s="63">
         <v>25</v>
       </c>
-      <c r="P21" s="63"/>
+      <c r="P21" s="63">
+        <v>25.1</v>
+      </c>
       <c r="Q21" s="63"/>
       <c r="R21" s="63"/>
       <c r="S21" s="63"/>
@@ -10952,7 +10984,7 @@
       <c r="AI21" s="63"/>
       <c r="AJ21" s="36">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="2"/>
@@ -11091,7 +11123,9 @@
       <c r="O23" s="63">
         <v>27.2</v>
       </c>
-      <c r="P23" s="63"/>
+      <c r="P23" s="63">
+        <v>30.2</v>
+      </c>
       <c r="Q23" s="63"/>
       <c r="R23" s="63"/>
       <c r="S23" s="63"/>
@@ -11113,7 +11147,7 @@
       <c r="AI23" s="63"/>
       <c r="AJ23" s="36">
         <f t="shared" si="1"/>
-        <v>27.2</v>
+        <v>30.2</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="2"/>
@@ -11186,7 +11220,9 @@
       <c r="O24" s="63">
         <v>28.3</v>
       </c>
-      <c r="P24" s="63"/>
+      <c r="P24" s="63">
+        <v>31</v>
+      </c>
       <c r="Q24" s="63"/>
       <c r="R24" s="63"/>
       <c r="S24" s="63"/>
@@ -11208,7 +11244,7 @@
       <c r="AI24" s="63"/>
       <c r="AJ24" s="36">
         <f t="shared" si="1"/>
-        <v>28.3</v>
+        <v>31</v>
       </c>
       <c r="AK24" s="21">
         <f t="shared" si="2"/>
@@ -11281,7 +11317,9 @@
       <c r="O25" s="63">
         <v>34.1</v>
       </c>
-      <c r="P25" s="63"/>
+      <c r="P25" s="63">
+        <v>36.200000000000003</v>
+      </c>
       <c r="Q25" s="63"/>
       <c r="R25" s="63"/>
       <c r="S25" s="63"/>
@@ -11303,18 +11341,18 @@
       <c r="AI25" s="63"/>
       <c r="AJ25" s="36">
         <f t="shared" si="1"/>
-        <v>34.1</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="2"/>
-        <v>36</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AL25" s="22">
         <v>36.799999999999997</v>
       </c>
       <c r="AM25" s="23">
         <f t="shared" si="3"/>
-        <v>-0.79999999999999716</v>
+        <v>-0.59999999999999432</v>
       </c>
       <c r="AN25" s="23">
         <v>30.83648877941982</v>
@@ -11376,7 +11414,9 @@
       <c r="O26" s="63">
         <v>20.6</v>
       </c>
-      <c r="P26" s="63"/>
+      <c r="P26" s="63">
+        <v>21.7</v>
+      </c>
       <c r="Q26" s="63"/>
       <c r="R26" s="63"/>
       <c r="S26" s="63"/>
@@ -11398,18 +11438,18 @@
       <c r="AI26" s="63"/>
       <c r="AJ26" s="36">
         <f t="shared" si="1"/>
-        <v>20.6</v>
+        <v>21.7</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="2"/>
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="AL26" s="22">
         <v>23.3</v>
       </c>
       <c r="AM26" s="23">
         <f t="shared" si="3"/>
-        <v>-1.9000000000000021</v>
+        <v>-1.6000000000000014</v>
       </c>
       <c r="AN26" s="23">
         <v>19.205027672249159</v>
@@ -11471,7 +11511,9 @@
       <c r="O27" s="63">
         <v>21</v>
       </c>
-      <c r="P27" s="63"/>
+      <c r="P27" s="63">
+        <v>23</v>
+      </c>
       <c r="Q27" s="63"/>
       <c r="R27" s="63"/>
       <c r="S27" s="63"/>
@@ -11493,18 +11535,18 @@
       <c r="AI27" s="63"/>
       <c r="AJ27" s="36">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="2"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL27" s="22">
         <v>23.4</v>
       </c>
       <c r="AM27" s="23">
         <f t="shared" si="3"/>
-        <v>-1.3999999999999986</v>
+        <v>-0.39999999999999858</v>
       </c>
       <c r="AN27" s="23">
         <v>18.093990147783249</v>
@@ -11566,7 +11608,9 @@
       <c r="O28" s="63">
         <v>30.7</v>
       </c>
-      <c r="P28" s="63"/>
+      <c r="P28" s="63">
+        <v>34.6</v>
+      </c>
       <c r="Q28" s="63"/>
       <c r="R28" s="63"/>
       <c r="S28" s="63"/>
@@ -11588,7 +11632,7 @@
       <c r="AI28" s="63"/>
       <c r="AJ28" s="36">
         <f t="shared" si="1"/>
-        <v>30.7</v>
+        <v>34.6</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="2"/>
@@ -11725,7 +11769,9 @@
       <c r="O30" s="63">
         <v>35</v>
       </c>
-      <c r="P30" s="63"/>
+      <c r="P30" s="63">
+        <v>36.299999999999997</v>
+      </c>
       <c r="Q30" s="63"/>
       <c r="R30" s="63"/>
       <c r="S30" s="63"/>
@@ -11747,7 +11793,7 @@
       <c r="AI30" s="63"/>
       <c r="AJ30" s="36">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="2"/>
@@ -11820,7 +11866,9 @@
       <c r="O31" s="63">
         <v>28.2</v>
       </c>
-      <c r="P31" s="63"/>
+      <c r="P31" s="63">
+        <v>28</v>
+      </c>
       <c r="Q31" s="63"/>
       <c r="R31" s="63"/>
       <c r="S31" s="63"/>
@@ -11842,7 +11890,7 @@
       <c r="AI31" s="63"/>
       <c r="AJ31" s="36">
         <f t="shared" si="1"/>
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="2"/>
@@ -11915,7 +11963,9 @@
       <c r="O32" s="63">
         <v>18.2</v>
       </c>
-      <c r="P32" s="63"/>
+      <c r="P32" s="63">
+        <v>19</v>
+      </c>
       <c r="Q32" s="63"/>
       <c r="R32" s="63"/>
       <c r="S32" s="63"/>
@@ -11937,7 +11987,7 @@
       <c r="AI32" s="63"/>
       <c r="AJ32" s="36">
         <f t="shared" si="1"/>
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="2"/>
@@ -12010,7 +12060,9 @@
       <c r="O33" s="63">
         <v>16.8</v>
       </c>
-      <c r="P33" s="63"/>
+      <c r="P33" s="63">
+        <v>17.399999999999999</v>
+      </c>
       <c r="Q33" s="63"/>
       <c r="R33" s="63"/>
       <c r="S33" s="63"/>
@@ -12032,7 +12084,7 @@
       <c r="AI33" s="63"/>
       <c r="AJ33" s="36">
         <f t="shared" si="1"/>
-        <v>16.8</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="2"/>
@@ -12157,7 +12209,9 @@
       <c r="O35" s="63">
         <v>29.2</v>
       </c>
-      <c r="P35" s="63"/>
+      <c r="P35" s="63">
+        <v>34.200000000000003</v>
+      </c>
       <c r="Q35" s="63"/>
       <c r="R35" s="63"/>
       <c r="S35" s="63"/>
@@ -12179,18 +12233,18 @@
       <c r="AI35" s="63"/>
       <c r="AJ35" s="36">
         <f t="shared" si="1"/>
-        <v>29.2</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="2"/>
-        <v>33.6</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="AL35" s="22">
         <v>35.200000000000003</v>
       </c>
       <c r="AM35" s="23">
         <f t="shared" si="3"/>
-        <v>-1.6000000000000014</v>
+        <v>-1</v>
       </c>
       <c r="AN35" s="23">
         <v>30.947113847837979</v>
@@ -12371,7 +12425,9 @@
       <c r="O38" s="63">
         <v>32.9</v>
       </c>
-      <c r="P38" s="63"/>
+      <c r="P38" s="63">
+        <v>31.8</v>
+      </c>
       <c r="Q38" s="63"/>
       <c r="R38" s="63"/>
       <c r="S38" s="63"/>
@@ -12393,7 +12449,7 @@
       <c r="AI38" s="63"/>
       <c r="AJ38" s="36">
         <f t="shared" si="1"/>
-        <v>32.9</v>
+        <v>31.8</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="2"/>
@@ -12467,7 +12523,9 @@
       <c r="O39" s="63">
         <v>34.4</v>
       </c>
-      <c r="P39" s="63"/>
+      <c r="P39" s="63">
+        <v>34.200000000000003</v>
+      </c>
       <c r="Q39" s="63"/>
       <c r="R39" s="63"/>
       <c r="S39" s="63"/>
@@ -12489,7 +12547,7 @@
       <c r="AI39" s="63"/>
       <c r="AJ39" s="36">
         <f t="shared" si="1"/>
-        <v>34.4</v>
+        <v>34.200000000000003</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="2"/>
@@ -12563,7 +12621,9 @@
       <c r="O40" s="63">
         <v>32.1</v>
       </c>
-      <c r="P40" s="63"/>
+      <c r="P40" s="63">
+        <v>31.4</v>
+      </c>
       <c r="Q40" s="63"/>
       <c r="R40" s="63"/>
       <c r="S40" s="63"/>
@@ -12585,7 +12645,7 @@
       <c r="AI40" s="63"/>
       <c r="AJ40" s="36">
         <f t="shared" si="1"/>
-        <v>32.1</v>
+        <v>31.4</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="2"/>
@@ -12659,7 +12719,9 @@
       <c r="O41" s="63">
         <v>27.2</v>
       </c>
-      <c r="P41" s="63"/>
+      <c r="P41" s="63">
+        <v>32</v>
+      </c>
       <c r="Q41" s="63"/>
       <c r="R41" s="63"/>
       <c r="S41" s="63"/>
@@ -12681,7 +12743,7 @@
       <c r="AI41" s="63"/>
       <c r="AJ41" s="36">
         <f t="shared" si="1"/>
-        <v>27.2</v>
+        <v>32</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="2"/>
@@ -12823,7 +12885,9 @@
       <c r="O43" s="63">
         <v>31.6</v>
       </c>
-      <c r="P43" s="63"/>
+      <c r="P43" s="63">
+        <v>32.6</v>
+      </c>
       <c r="Q43" s="63"/>
       <c r="R43" s="63"/>
       <c r="S43" s="63"/>
@@ -12845,7 +12909,7 @@
       <c r="AI43" s="63"/>
       <c r="AJ43" s="36">
         <f t="shared" si="1"/>
-        <v>31.6</v>
+        <v>32.6</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="2"/>
@@ -12919,7 +12983,9 @@
       <c r="O44" s="29">
         <v>33.200000000000003</v>
       </c>
-      <c r="P44" s="29"/>
+      <c r="P44" s="29">
+        <v>32.200000000000003</v>
+      </c>
       <c r="Q44" s="29"/>
       <c r="R44" s="29"/>
       <c r="S44" s="29"/>
@@ -12941,7 +13007,7 @@
       <c r="AI44" s="63"/>
       <c r="AJ44" s="36">
         <f t="shared" si="1"/>
-        <v>33.200000000000003</v>
+        <v>32.200000000000003</v>
       </c>
       <c r="AK44" s="21">
         <f t="shared" si="2"/>
@@ -13015,7 +13081,9 @@
       <c r="O45" s="63">
         <v>32.6</v>
       </c>
-      <c r="P45" s="63"/>
+      <c r="P45" s="63">
+        <v>32.799999999999997</v>
+      </c>
       <c r="Q45" s="63"/>
       <c r="R45" s="63"/>
       <c r="S45" s="63"/>
@@ -13037,7 +13105,7 @@
       <c r="AI45" s="63"/>
       <c r="AJ45" s="36">
         <f t="shared" si="1"/>
-        <v>32.6</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="2"/>
@@ -13243,7 +13311,9 @@
       <c r="O48" s="63">
         <v>31.5</v>
       </c>
-      <c r="P48" s="63"/>
+      <c r="P48" s="63">
+        <v>31</v>
+      </c>
       <c r="Q48" s="63"/>
       <c r="R48" s="63"/>
       <c r="S48" s="63"/>
@@ -13265,7 +13335,7 @@
       <c r="AI48" s="63"/>
       <c r="AJ48" s="36">
         <f t="shared" si="1"/>
-        <v>31.5</v>
+        <v>31</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="2"/>
@@ -26343,12 +26413,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -26358,6 +26422,12 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
